--- a/testdata/enthuse_example.xlsx
+++ b/testdata/enthuse_example.xlsx
@@ -100,7 +100,7 @@
     <t xml:space="preserve">Payment</t>
   </si>
   <si>
-    <t xml:space="preserve">py_2SZANObc13bvgL6ja</t>
+    <t xml:space="preserve">py_abcdef2SZANN6oA613bvgL6ja</t>
   </si>
   <si>
     <t xml:space="preserve">xxx</t>
@@ -121,13 +121,13 @@
     <t xml:space="preserve">Monthly</t>
   </si>
   <si>
-    <t xml:space="preserve">py_2Saionabc0yICk10Qb</t>
+    <t xml:space="preserve">py_abcdef2Saion6OM60yICk10Qb</t>
   </si>
   <si>
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
-    <t xml:space="preserve">ch_2Sbdefg26OMOHD7c</t>
+    <t xml:space="preserve">ch_abcdef2Sb8q26OA60KAgOHD7c</t>
   </si>
   <si>
     <t xml:space="preserve">Anonymous</t>
@@ -221,20 +221,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -495,264 +487,264 @@
   <dimension ref="A1:X4"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="28.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="28.89"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="0" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>45995.0165046296</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="1" t="n">
+        <v>45965.0165046296</v>
+      </c>
+      <c r="C2" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="1" t="n">
-        <v>8157399</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="E2" s="0" t="n">
+        <v>9157399</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="1" t="n">
+      <c r="L2" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="M2" s="0" t="n">
         <v>0.4</v>
       </c>
-      <c r="N2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="1" t="n">
+      <c r="N2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="0" t="n">
         <v>4.6</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="Q2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="1" t="s">
+      <c r="Q2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="S2" s="1" t="n">
+      <c r="S2" s="0" t="n">
         <v>123457</v>
       </c>
-      <c r="V2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" s="1" t="n">
+      <c r="V2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>45995.8389236111</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="1" t="n">
+        <v>45965.8389236111</v>
+      </c>
+      <c r="C3" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>8157398</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="E3" s="0" t="n">
+        <v>9157398</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="1" t="n">
+      <c r="L3" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="M3" s="1" t="n">
+      <c r="M3" s="0" t="n">
         <v>0.62</v>
       </c>
-      <c r="N3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="1" t="n">
+      <c r="N3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="0" t="n">
         <v>9.38</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="P3" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="Q3" s="1" t="n">
+      <c r="Q3" s="0" t="n">
         <v>2.5</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="R3" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="S3" s="1" t="n">
+      <c r="S3" s="0" t="n">
         <v>123456</v>
       </c>
-      <c r="V3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="1" t="n">
+      <c r="V3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>45996.9965856482</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="1" t="n">
+        <v>45966.9965856482</v>
+      </c>
+      <c r="C4" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>6848690</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="E4" s="0" t="n">
+        <v>9848690</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="L4" s="1" t="n">
+      <c r="L4" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="M4" s="0" t="n">
         <v>0.62</v>
       </c>
-      <c r="N4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="1" t="n">
+      <c r="N4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="0" t="n">
         <v>9.38</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="P4" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="Q4" s="1" t="n">
+      <c r="Q4" s="0" t="n">
         <v>2.5</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="R4" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="S4" s="1" t="n">
+      <c r="S4" s="0" t="n">
         <v>123455</v>
       </c>
-      <c r="V4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="1" t="n">
+      <c r="V4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="0" t="n">
         <v>0</v>
       </c>
     </row>
